--- a/Stocks/Nifty_500_2025_Apr_20_stocks_results/master_momentum_summary.xlsx
+++ b/Stocks/Nifty_500_2025_Apr_20_stocks_results/master_momentum_summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D761"/>
+  <dimension ref="A1:D801"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>INE463V01026</t>
+          <t>INE732I01013</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>INE732I01013</t>
+          <t>INE463V01026</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -15647,6 +15647,806 @@
         </is>
       </c>
       <c r="D761" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>INE139A01034</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>INE205A01025</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>INE084A01016</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>INE721A01047</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>INE038A01020</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>INE062A01020</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>INE774D01024</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>INE562A01011</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>INE171A01029</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>INE531E01026</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>INE208A01029</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D772" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>INE476A01022</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D773" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>INE745G01035</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D774" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>INE692A01016</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D775" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>INE292B01021</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="D776" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>INE238A01034</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="D777" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>INE267A01025</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>HINDZINC</t>
+        </is>
+      </c>
+      <c r="D778" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>INE414G01012</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>MUTHOOTFIN</t>
+        </is>
+      </c>
+      <c r="D779" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>INE573A01042</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>JKTYRE</t>
+        </is>
+      </c>
+      <c r="D780" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>INE114A01011</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D781" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>INE205A01025</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>VEDL</t>
+        </is>
+      </c>
+      <c r="D782" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>INE084A01016</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="D783" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>INE465A01025</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>BHARATFORG</t>
+        </is>
+      </c>
+      <c r="D784" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>INE208A01029</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>ASHOKLEY</t>
+        </is>
+      </c>
+      <c r="D785" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>INE139A01034</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="D786" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>INE692A01016</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="D787" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>INE062A01020</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="D788" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>INE721A01047</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="D789" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>INE562A01011</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="D790" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>INE171A01029</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="D791" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>INE745G01035</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="D792" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>INE476A01022</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="D793" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>INE774D01024</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>M&amp;MFIN</t>
+        </is>
+      </c>
+      <c r="D794" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>INE531E01026</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>HINDCOPPER</t>
+        </is>
+      </c>
+      <c r="D795" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>INE114A01011</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="D796" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>INE457A01014</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>MAHABANK</t>
+        </is>
+      </c>
+      <c r="D797" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>INE038A01020</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="D798" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>INE242A01010</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>IOC</t>
+        </is>
+      </c>
+      <c r="D799" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>INE028A01039</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="D800" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>INE702C01027</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="D801" t="n">
         <v>20</v>
       </c>
     </row>
